--- a/Team-Data/2013-14/3-1-2013-14.xlsx
+++ b/Team-Data/2013-14/3-1-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-0.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
@@ -751,7 +818,7 @@
         <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI2" t="n">
         <v>16</v>
@@ -763,13 +830,13 @@
         <v>7</v>
       </c>
       <c r="AL2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM2" t="n">
         <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AO2" t="n">
         <v>20</v>
@@ -793,7 +860,7 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
         <v>7</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E3" t="n">
         <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.333</v>
+        <v>0.339</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
@@ -861,7 +928,7 @@
         <v>36.4</v>
       </c>
       <c r="J3" t="n">
-        <v>83.8</v>
+        <v>83.7</v>
       </c>
       <c r="K3" t="n">
         <v>0.435</v>
@@ -870,7 +937,7 @@
         <v>6.4</v>
       </c>
       <c r="M3" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N3" t="n">
         <v>0.327</v>
@@ -882,7 +949,7 @@
         <v>21.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.769</v>
+        <v>0.768</v>
       </c>
       <c r="R3" t="n">
         <v>11.7</v>
@@ -894,13 +961,13 @@
         <v>43</v>
       </c>
       <c r="U3" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V3" t="n">
         <v>15.4</v>
       </c>
       <c r="W3" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X3" t="n">
         <v>4.5</v>
@@ -915,25 +982,25 @@
         <v>19.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.5</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC3" t="n">
         <v>-3.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
         <v>25</v>
       </c>
       <c r="AF3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
         <v>23</v>
@@ -972,13 +1039,13 @@
         <v>15</v>
       </c>
       <c r="AU3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW3" t="n">
         <v>21</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>22</v>
       </c>
       <c r="AX3" t="n">
         <v>19</v>
@@ -993,7 +1060,7 @@
         <v>27</v>
       </c>
       <c r="BB3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC3" t="n">
         <v>24</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F4" t="n">
         <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>0.491</v>
+        <v>0.482</v>
       </c>
       <c r="H4" t="n">
         <v>48.4</v>
@@ -1043,7 +1110,7 @@
         <v>35.3</v>
       </c>
       <c r="J4" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K4" t="n">
         <v>0.45</v>
@@ -1052,28 +1119,28 @@
         <v>8</v>
       </c>
       <c r="M4" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.361</v>
+        <v>0.36</v>
       </c>
       <c r="O4" t="n">
         <v>18.8</v>
       </c>
       <c r="P4" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="R4" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="S4" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T4" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="U4" t="n">
         <v>20.7</v>
@@ -1082,28 +1149,28 @@
         <v>14.5</v>
       </c>
       <c r="W4" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y4" t="n">
         <v>4.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA4" t="n">
         <v>20.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>97.5</v>
+        <v>97.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.2</v>
+        <v>-2.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE4" t="n">
         <v>16</v>
@@ -1127,7 +1194,7 @@
         <v>15</v>
       </c>
       <c r="AL4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM4" t="n">
         <v>12</v>
@@ -1139,13 +1206,13 @@
         <v>8</v>
       </c>
       <c r="AP4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS4" t="n">
         <v>28</v>
@@ -1163,7 +1230,7 @@
         <v>11</v>
       </c>
       <c r="AX4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY4" t="n">
         <v>8</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -1285,10 +1352,10 @@
         <v>-1.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AE5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF5" t="n">
         <v>17</v>
@@ -1297,7 +1364,7 @@
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI5" t="n">
         <v>27</v>
@@ -1315,7 +1382,7 @@
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO5" t="n">
         <v>12</v>
@@ -1324,16 +1391,16 @@
         <v>7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS5" t="n">
         <v>7</v>
       </c>
       <c r="AT5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU5" t="n">
         <v>19</v>
@@ -1351,7 +1418,7 @@
         <v>21</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -1467,10 +1534,10 @@
         <v>0.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AE6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF6" t="n">
         <v>12</v>
@@ -1491,13 +1558,13 @@
         <v>28</v>
       </c>
       <c r="AL6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM6" t="n">
         <v>27</v>
       </c>
       <c r="AN6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO6" t="n">
         <v>13</v>
@@ -1527,7 +1594,7 @@
         <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY6" t="n">
         <v>29</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -1571,43 +1638,43 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
         <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G7" t="n">
-        <v>0.393</v>
+        <v>0.4</v>
       </c>
       <c r="H7" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I7" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J7" t="n">
-        <v>85.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.426</v>
+        <v>0.425</v>
       </c>
       <c r="L7" t="n">
         <v>7</v>
       </c>
       <c r="M7" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N7" t="n">
         <v>0.351</v>
       </c>
       <c r="O7" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="P7" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="Q7" t="n">
         <v>0.75</v>
@@ -1616,37 +1683,37 @@
         <v>12.8</v>
       </c>
       <c r="S7" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T7" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="U7" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V7" t="n">
         <v>14.4</v>
       </c>
       <c r="W7" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X7" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z7" t="n">
         <v>20</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB7" t="n">
         <v>97</v>
       </c>
       <c r="AC7" t="n">
-        <v>-4.2</v>
+        <v>-4</v>
       </c>
       <c r="AD7" t="n">
         <v>1</v>
@@ -1664,7 +1731,7 @@
         <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ7" t="n">
         <v>5</v>
@@ -1691,7 +1758,7 @@
         <v>20</v>
       </c>
       <c r="AR7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS7" t="n">
         <v>15</v>
@@ -1718,7 +1785,7 @@
         <v>9</v>
       </c>
       <c r="BA7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB7" t="n">
         <v>23</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>8</v>
@@ -1843,7 +1910,7 @@
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
@@ -1885,7 +1952,7 @@
         <v>4</v>
       </c>
       <c r="AV8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW8" t="n">
         <v>3</v>
@@ -1900,10 +1967,10 @@
         <v>10</v>
       </c>
       <c r="BA8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -1935,22 +2002,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E9" t="n">
         <v>25</v>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G9" t="n">
-        <v>0.431</v>
+        <v>0.439</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
       </c>
       <c r="I9" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="J9" t="n">
         <v>85.2</v>
@@ -1965,37 +2032,37 @@
         <v>23</v>
       </c>
       <c r="N9" t="n">
-        <v>0.357</v>
+        <v>0.358</v>
       </c>
       <c r="O9" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P9" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.717</v>
+        <v>0.719</v>
       </c>
       <c r="R9" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S9" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="T9" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
       <c r="U9" t="n">
         <v>21.6</v>
       </c>
       <c r="V9" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W9" t="n">
         <v>7.1</v>
       </c>
       <c r="X9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y9" t="n">
         <v>5.6</v>
@@ -2004,16 +2071,16 @@
         <v>22.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.2</v>
+        <v>102.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.5</v>
+        <v>-2.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AE9" t="n">
         <v>19</v>
@@ -2028,13 +2095,13 @@
         <v>27</v>
       </c>
       <c r="AI9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AJ9" t="n">
         <v>6</v>
       </c>
       <c r="AK9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL9" t="n">
         <v>11</v>
@@ -2043,7 +2110,7 @@
         <v>9</v>
       </c>
       <c r="AN9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO9" t="n">
         <v>9</v>
@@ -2064,7 +2131,7 @@
         <v>5</v>
       </c>
       <c r="AU9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV9" t="n">
         <v>25</v>
@@ -2073,7 +2140,7 @@
         <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY9" t="n">
         <v>23</v>
@@ -2088,7 +2155,7 @@
         <v>11</v>
       </c>
       <c r="BC9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -2117,25 +2184,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>0.39</v>
+        <v>0.397</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="J10" t="n">
-        <v>86.7</v>
+        <v>86.5</v>
       </c>
       <c r="K10" t="n">
         <v>0.45</v>
@@ -2147,28 +2214,28 @@
         <v>18.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.312</v>
+        <v>0.313</v>
       </c>
       <c r="O10" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P10" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.666</v>
+        <v>0.664</v>
       </c>
       <c r="R10" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="S10" t="n">
         <v>30.4</v>
       </c>
       <c r="T10" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
       <c r="U10" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V10" t="n">
         <v>15</v>
@@ -2183,19 +2250,19 @@
         <v>4.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA10" t="n">
         <v>20.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>101</v>
+        <v>100.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.8</v>
+        <v>-2.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2207,10 +2274,10 @@
         <v>21</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ10" t="n">
         <v>4</v>
@@ -2246,7 +2313,7 @@
         <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV10" t="n">
         <v>17</v>
@@ -2258,7 +2325,7 @@
         <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ10" t="n">
         <v>15</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,7 +2456,7 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
         <v>7</v>
@@ -2398,7 +2465,7 @@
         <v>7</v>
       </c>
       <c r="AK11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL11" t="n">
         <v>5</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -2481,34 +2548,34 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F12" t="n">
         <v>19</v>
       </c>
       <c r="G12" t="n">
-        <v>0.678</v>
+        <v>0.672</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J12" t="n">
-        <v>79.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.475</v>
+        <v>0.474</v>
       </c>
       <c r="L12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="M12" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="N12" t="n">
         <v>0.354</v>
@@ -2526,13 +2593,13 @@
         <v>11.2</v>
       </c>
       <c r="S12" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="T12" t="n">
         <v>45.3</v>
       </c>
       <c r="U12" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V12" t="n">
         <v>16.5</v>
@@ -2553,13 +2620,13 @@
         <v>24.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.4</v>
+        <v>106.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -2571,7 +2638,7 @@
         <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI12" t="n">
         <v>14</v>
@@ -2619,7 +2686,7 @@
         <v>18</v>
       </c>
       <c r="AX12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY12" t="n">
         <v>20</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -2663,34 +2730,34 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F13" t="n">
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>0.776</v>
+        <v>0.772</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J13" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L13" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M13" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="N13" t="n">
         <v>0.353</v>
@@ -2705,19 +2772,19 @@
         <v>0.781</v>
       </c>
       <c r="R13" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S13" t="n">
         <v>35.3</v>
       </c>
       <c r="T13" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
       <c r="U13" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V13" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W13" t="n">
         <v>7.2</v>
@@ -2741,7 +2808,7 @@
         <v>8</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2762,7 +2829,7 @@
         <v>25</v>
       </c>
       <c r="AK13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL13" t="n">
         <v>21</v>
@@ -2771,13 +2838,13 @@
         <v>23</v>
       </c>
       <c r="AN13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO13" t="n">
         <v>11</v>
       </c>
       <c r="AP13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
         <v>5</v>
@@ -2795,13 +2862,13 @@
         <v>24</v>
       </c>
       <c r="AV13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY13" t="n">
         <v>11</v>
@@ -2813,7 +2880,7 @@
         <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC13" t="n">
         <v>1</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E14" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F14" t="n">
         <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.672</v>
+        <v>0.667</v>
       </c>
       <c r="H14" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I14" t="n">
         <v>38.6</v>
       </c>
       <c r="J14" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>0.472</v>
@@ -2890,16 +2957,16 @@
         <v>10.4</v>
       </c>
       <c r="S14" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T14" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U14" t="n">
         <v>24.2</v>
       </c>
       <c r="V14" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W14" t="n">
         <v>8.4</v>
@@ -2908,19 +2975,19 @@
         <v>4.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Z14" t="n">
         <v>21.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="AB14" t="n">
         <v>107.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
@@ -2953,7 +3020,7 @@
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO14" t="n">
         <v>2</v>
@@ -2977,7 +3044,7 @@
         <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW14" t="n">
         <v>9</v>
@@ -2998,7 +3065,7 @@
         <v>2</v>
       </c>
       <c r="BC14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -3105,16 +3172,16 @@
         <v>-5.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
       </c>
       <c r="AF15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH15" t="n">
         <v>28</v>
@@ -3129,7 +3196,7 @@
         <v>17</v>
       </c>
       <c r="AL15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM15" t="n">
         <v>6</v>
@@ -3156,10 +3223,10 @@
         <v>23</v>
       </c>
       <c r="AU15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW15" t="n">
         <v>28</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -3209,58 +3276,58 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F16" t="n">
         <v>25</v>
       </c>
       <c r="G16" t="n">
-        <v>0.569</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J16" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.459</v>
+        <v>0.457</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="M16" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.351</v>
+        <v>0.348</v>
       </c>
       <c r="O16" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="P16" t="n">
         <v>20.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.75</v>
+        <v>0.751</v>
       </c>
       <c r="R16" t="n">
         <v>11.4</v>
       </c>
       <c r="S16" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T16" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U16" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V16" t="n">
         <v>13.5</v>
@@ -3272,22 +3339,22 @@
         <v>4.7</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="AA16" t="n">
         <v>18.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>95.5</v>
+        <v>95.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3302,13 +3369,13 @@
         <v>13</v>
       </c>
       <c r="AI16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AJ16" t="n">
         <v>21</v>
       </c>
       <c r="AK16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AO16" t="n">
         <v>29</v>
@@ -3326,7 +3393,7 @@
         <v>28</v>
       </c>
       <c r="AQ16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR16" t="n">
         <v>14</v>
@@ -3335,22 +3402,22 @@
         <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AU16" t="n">
         <v>13</v>
       </c>
       <c r="AV16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW16" t="n">
         <v>16</v>
       </c>
       <c r="AX16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ16" t="n">
         <v>7</v>
@@ -3359,7 +3426,7 @@
         <v>30</v>
       </c>
       <c r="BB16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC16" t="n">
         <v>15</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -3391,34 +3458,34 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F17" t="n">
         <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.75</v>
+        <v>0.745</v>
       </c>
       <c r="H17" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I17" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="J17" t="n">
-        <v>76.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.511</v>
+        <v>0.509</v>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M17" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="N17" t="n">
         <v>0.369</v>
@@ -3430,10 +3497,10 @@
         <v>23.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.758</v>
+        <v>0.756</v>
       </c>
       <c r="R17" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="S17" t="n">
         <v>29.4</v>
@@ -3442,16 +3509,16 @@
         <v>36.8</v>
       </c>
       <c r="U17" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="V17" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W17" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y17" t="n">
         <v>3</v>
@@ -3463,22 +3530,22 @@
         <v>20.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>104.4</v>
+        <v>104.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="AD17" t="n">
         <v>30</v>
       </c>
       <c r="AE17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF17" t="n">
         <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH17" t="n">
         <v>9</v>
@@ -3505,7 +3572,7 @@
         <v>14</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
         <v>16</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AV17" t="n">
         <v>16</v>
@@ -3541,10 +3608,10 @@
         <v>12</v>
       </c>
       <c r="BB17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -3573,25 +3640,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E18" t="n">
         <v>11</v>
       </c>
       <c r="F18" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G18" t="n">
-        <v>0.19</v>
+        <v>0.193</v>
       </c>
       <c r="H18" t="n">
         <v>48.6</v>
       </c>
       <c r="I18" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="J18" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="K18" t="n">
         <v>0.426</v>
@@ -3600,19 +3667,19 @@
         <v>7.4</v>
       </c>
       <c r="M18" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="N18" t="n">
         <v>0.358</v>
       </c>
       <c r="O18" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="P18" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.752</v>
+        <v>0.751</v>
       </c>
       <c r="R18" t="n">
         <v>11.7</v>
@@ -3624,7 +3691,7 @@
         <v>41.3</v>
       </c>
       <c r="U18" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V18" t="n">
         <v>15.5</v>
@@ -3636,22 +3703,22 @@
         <v>5.3</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z18" t="n">
         <v>20.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>93.40000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="AC18" t="n">
         <v>-8.699999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3681,7 +3748,7 @@
         <v>17</v>
       </c>
       <c r="AN18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO18" t="n">
         <v>28</v>
@@ -3690,7 +3757,7 @@
         <v>27</v>
       </c>
       <c r="AQ18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AR18" t="n">
         <v>12</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F19" t="n">
         <v>29</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.491</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3773,25 +3840,25 @@
         <v>38.5</v>
       </c>
       <c r="J19" t="n">
-        <v>87.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L19" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M19" t="n">
         <v>22</v>
       </c>
       <c r="N19" t="n">
-        <v>0.342</v>
+        <v>0.344</v>
       </c>
       <c r="O19" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="P19" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="Q19" t="n">
         <v>0.775</v>
@@ -3800,40 +3867,40 @@
         <v>12.8</v>
       </c>
       <c r="S19" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T19" t="n">
         <v>45.6</v>
       </c>
       <c r="U19" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="V19" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="W19" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X19" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y19" t="n">
         <v>5.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="AB19" t="n">
         <v>105.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD19" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AE19" t="n">
         <v>15</v>
@@ -3848,7 +3915,7 @@
         <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ19" t="n">
         <v>2</v>
@@ -3863,7 +3930,7 @@
         <v>13</v>
       </c>
       <c r="AN19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO19" t="n">
         <v>3</v>
@@ -3875,10 +3942,10 @@
         <v>8</v>
       </c>
       <c r="AR19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT19" t="n">
         <v>4</v>
@@ -3899,7 +3966,7 @@
         <v>26</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA19" t="n">
         <v>3</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -3937,85 +4004,85 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E20" t="n">
         <v>23</v>
       </c>
       <c r="F20" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G20" t="n">
-        <v>0.39</v>
+        <v>0.397</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>37.8</v>
+        <v>38</v>
       </c>
       <c r="J20" t="n">
-        <v>83.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.455</v>
+        <v>0.457</v>
       </c>
       <c r="L20" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M20" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.38</v>
+        <v>0.385</v>
       </c>
       <c r="O20" t="n">
         <v>17.2</v>
       </c>
       <c r="P20" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.764</v>
+        <v>0.762</v>
       </c>
       <c r="R20" t="n">
         <v>12</v>
       </c>
       <c r="S20" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T20" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U20" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V20" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W20" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X20" t="n">
         <v>6.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>98.8</v>
+        <v>99.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>-2.9</v>
+        <v>-2.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE20" t="n">
         <v>21</v>
@@ -4027,7 +4094,7 @@
         <v>21</v>
       </c>
       <c r="AH20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI20" t="n">
         <v>13</v>
@@ -4036,16 +4103,16 @@
         <v>14</v>
       </c>
       <c r="AK20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AL20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM20" t="n">
         <v>29</v>
       </c>
       <c r="AN20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AO20" t="n">
         <v>16</v>
@@ -4054,7 +4121,7 @@
         <v>18</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AR20" t="n">
         <v>7</v>
@@ -4063,13 +4130,13 @@
         <v>26</v>
       </c>
       <c r="AT20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AU20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW20" t="n">
         <v>12</v>
@@ -4084,13 +4151,13 @@
         <v>27</v>
       </c>
       <c r="BA20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC20" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-2.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
         <v>23</v>
@@ -4209,7 +4276,7 @@
         <v>24</v>
       </c>
       <c r="AH21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR21" t="n">
         <v>19</v>
@@ -4248,7 +4315,7 @@
         <v>26</v>
       </c>
       <c r="AU21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV21" t="n">
         <v>2</v>
@@ -4272,7 +4339,7 @@
         <v>21</v>
       </c>
       <c r="BC21" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -4379,22 +4446,22 @@
         <v>6.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="n">
         <v>3</v>
       </c>
       <c r="AG22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="n">
         <v>26</v>
       </c>
       <c r="AI22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ22" t="n">
         <v>19</v>
@@ -4430,7 +4497,7 @@
         <v>8</v>
       </c>
       <c r="AU22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV22" t="n">
         <v>28</v>
@@ -4454,7 +4521,7 @@
         <v>5</v>
       </c>
       <c r="BC22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -4483,19 +4550,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
         <v>18</v>
       </c>
       <c r="F23" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G23" t="n">
-        <v>0.295</v>
+        <v>0.3</v>
       </c>
       <c r="H23" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I23" t="n">
         <v>36.7</v>
@@ -4507,43 +4574,43 @@
         <v>0.442</v>
       </c>
       <c r="L23" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M23" t="n">
         <v>19.9</v>
       </c>
       <c r="N23" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="O23" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P23" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="Q23" t="n">
         <v>0.764</v>
       </c>
       <c r="R23" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="S23" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T23" t="n">
         <v>42.3</v>
       </c>
       <c r="U23" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V23" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W23" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y23" t="n">
         <v>5.8</v>
@@ -4558,7 +4625,7 @@
         <v>96.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.2</v>
+        <v>-5.1</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4582,7 +4649,7 @@
         <v>16</v>
       </c>
       <c r="AK23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="n">
         <v>19</v>
@@ -4591,28 +4658,28 @@
         <v>20</v>
       </c>
       <c r="AN23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP23" t="n">
         <v>24</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR23" t="n">
         <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU23" t="n">
         <v>20</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>21</v>
       </c>
       <c r="AV23" t="n">
         <v>12</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24" t="n">
         <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G24" t="n">
-        <v>0.254</v>
+        <v>0.259</v>
       </c>
       <c r="H24" t="n">
         <v>48.6</v>
@@ -4689,19 +4756,19 @@
         <v>0.434</v>
       </c>
       <c r="L24" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M24" t="n">
         <v>21.9</v>
       </c>
       <c r="N24" t="n">
-        <v>0.308</v>
+        <v>0.309</v>
       </c>
       <c r="O24" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P24" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="Q24" t="n">
         <v>0.715</v>
@@ -4713,7 +4780,7 @@
         <v>32.1</v>
       </c>
       <c r="T24" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
       <c r="U24" t="n">
         <v>22.1</v>
@@ -4725,7 +4792,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y24" t="n">
         <v>7.4</v>
@@ -4737,13 +4804,13 @@
         <v>20.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>100.3</v>
+        <v>100.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>-10.8</v>
+        <v>-10.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4755,7 +4822,7 @@
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI24" t="n">
         <v>12</v>
@@ -4767,7 +4834,7 @@
         <v>27</v>
       </c>
       <c r="AL24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM24" t="n">
         <v>14</v>
@@ -4779,7 +4846,7 @@
         <v>19</v>
       </c>
       <c r="AP24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
@@ -4803,7 +4870,7 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY24" t="n">
         <v>30</v>
@@ -4815,7 +4882,7 @@
         <v>13</v>
       </c>
       <c r="BB24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
@@ -4937,7 +5004,7 @@
         <v>10</v>
       </c>
       <c r="AH25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI25" t="n">
         <v>9</v>
@@ -4946,7 +5013,7 @@
         <v>9</v>
       </c>
       <c r="AK25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL25" t="n">
         <v>4</v>
@@ -4970,7 +5037,7 @@
         <v>13</v>
       </c>
       <c r="AS25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT25" t="n">
         <v>13</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -5029,37 +5096,37 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F26" t="n">
         <v>18</v>
       </c>
       <c r="G26" t="n">
-        <v>0.695</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="J26" t="n">
-        <v>87.7</v>
+        <v>87.8</v>
       </c>
       <c r="K26" t="n">
         <v>0.452</v>
       </c>
       <c r="L26" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="M26" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.378</v>
+        <v>0.382</v>
       </c>
       <c r="O26" t="n">
         <v>19.2</v>
@@ -5068,19 +5135,19 @@
         <v>23.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.826</v>
+        <v>0.824</v>
       </c>
       <c r="R26" t="n">
         <v>12.6</v>
       </c>
       <c r="S26" t="n">
-        <v>33.7</v>
+        <v>33.5</v>
       </c>
       <c r="T26" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
       <c r="U26" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="V26" t="n">
         <v>13.7</v>
@@ -5095,19 +5162,19 @@
         <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AA26" t="n">
         <v>20.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>107.8</v>
+        <v>107.9</v>
       </c>
       <c r="AC26" t="n">
         <v>4.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
         <v>5</v>
@@ -5119,7 +5186,7 @@
         <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
@@ -5131,13 +5198,13 @@
         <v>14</v>
       </c>
       <c r="AL26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM26" t="n">
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AO26" t="n">
         <v>6</v>
@@ -5167,7 +5234,7 @@
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY26" t="n">
         <v>5</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E27" t="n">
         <v>20</v>
       </c>
       <c r="F27" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G27" t="n">
-        <v>0.339</v>
+        <v>0.345</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5238,19 +5305,19 @@
         <v>6.6</v>
       </c>
       <c r="M27" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="N27" t="n">
-        <v>0.344</v>
+        <v>0.345</v>
       </c>
       <c r="O27" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="P27" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.777</v>
+        <v>0.778</v>
       </c>
       <c r="R27" t="n">
         <v>11.9</v>
@@ -5259,16 +5326,16 @@
         <v>31.7</v>
       </c>
       <c r="T27" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="U27" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="V27" t="n">
         <v>15.1</v>
       </c>
       <c r="W27" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X27" t="n">
         <v>4</v>
@@ -5277,25 +5344,25 @@
         <v>5.7</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AA27" t="n">
         <v>22.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>101.6</v>
+        <v>101.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.5</v>
+        <v>-2.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG27" t="n">
         <v>25</v>
@@ -5334,7 +5401,7 @@
         <v>8</v>
       </c>
       <c r="AS27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT27" t="n">
         <v>12</v>
@@ -5355,7 +5422,7 @@
         <v>24</v>
       </c>
       <c r="AZ27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA27" t="n">
         <v>4</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>6</v>
       </c>
       <c r="AD28" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5483,7 +5550,7 @@
         <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
@@ -5495,16 +5562,16 @@
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN28" t="n">
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP28" t="n">
         <v>29</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -5653,10 +5720,10 @@
         <v>3</v>
       </c>
       <c r="AD29" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AE29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF29" t="n">
         <v>12</v>
@@ -5668,7 +5735,7 @@
         <v>4</v>
       </c>
       <c r="AI29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ29" t="n">
         <v>18</v>
@@ -5689,7 +5756,7 @@
         <v>7</v>
       </c>
       <c r="AP29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ29" t="n">
         <v>9</v>
@@ -5704,7 +5771,7 @@
         <v>14</v>
       </c>
       <c r="AU29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
@@ -5719,7 +5786,7 @@
         <v>13</v>
       </c>
       <c r="AZ29" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA29" t="n">
         <v>5</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -5835,19 +5902,19 @@
         <v>-5.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AE30" t="n">
         <v>23</v>
       </c>
       <c r="AF30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG30" t="n">
         <v>23</v>
       </c>
       <c r="AH30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI30" t="n">
         <v>26</v>
@@ -5856,7 +5923,7 @@
         <v>26</v>
       </c>
       <c r="AK30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL30" t="n">
         <v>22</v>
@@ -5868,7 +5935,7 @@
         <v>17</v>
       </c>
       <c r="AO30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP30" t="n">
         <v>21</v>
@@ -5895,7 +5962,7 @@
         <v>26</v>
       </c>
       <c r="AX30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY30" t="n">
         <v>16</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
@@ -5939,43 +6006,43 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F31" t="n">
         <v>28</v>
       </c>
       <c r="G31" t="n">
-        <v>0.525</v>
+        <v>0.517</v>
       </c>
       <c r="H31" t="n">
         <v>49</v>
       </c>
       <c r="I31" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="J31" t="n">
         <v>84.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L31" t="n">
         <v>7.8</v>
       </c>
       <c r="M31" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.382</v>
+        <v>0.38</v>
       </c>
       <c r="O31" t="n">
         <v>15.6</v>
       </c>
       <c r="P31" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="Q31" t="n">
         <v>0.728</v>
@@ -5990,34 +6057,34 @@
         <v>42.6</v>
       </c>
       <c r="U31" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="V31" t="n">
         <v>14.7</v>
       </c>
       <c r="W31" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X31" t="n">
         <v>4.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA31" t="n">
         <v>19.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>100.6</v>
+        <v>100.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6032,7 +6099,7 @@
         <v>1</v>
       </c>
       <c r="AI31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ31" t="n">
         <v>8</v>
@@ -6047,16 +6114,16 @@
         <v>18</v>
       </c>
       <c r="AN31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP31" t="n">
         <v>23</v>
       </c>
       <c r="AQ31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR31" t="n">
         <v>18</v>
@@ -6068,7 +6135,7 @@
         <v>17</v>
       </c>
       <c r="AU31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV31" t="n">
         <v>14</v>
@@ -6086,10 +6153,10 @@
         <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC31" t="n">
         <v>14</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-1-2013-14</t>
+          <t>2014-03-01</t>
         </is>
       </c>
     </row>
